--- a/output/2026-summer_夏合宿収支報告.xlsx
+++ b/output/2026-summer_夏合宿収支報告.xlsx
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>22024</v>
+        <v>25894</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1047,16 +1047,16 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>コメリ真田店</t>
+          <t>セブンイレブン菅平高原八店</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>消臭剤・HDMIケーブル</t>
+          <t>串団子3本入 23パック</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>2178</v>
+        <v>3179</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -1068,7 +1068,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>補食。昨年台帳でも団子は雑費計上</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="n">
@@ -1084,11 +1088,11 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>ゼリー飲料3点</t>
+          <t>串団子3本入 5パック</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>878</v>
+        <v>691</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
@@ -1100,27 +1104,31 @@
           <t>未</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>補食。昨年台帳でも団子は雑費計上</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
-        <v>46240</v>
+        <v>46236</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>セブンイレブン菅平高原八店</t>
+          <t>コメリ真田店</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>内訳記載なし（クレジット払い）</t>
+          <t>消臭剤・HDMIケーブル</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>14631</v>
+        <v>2178</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -1132,15 +1140,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>品目不明。要メモ</t>
-        </is>
-      </c>
+      <c r="H6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n">
-        <v>46240</v>
+        <v>46236</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>4</v>
@@ -1152,11 +1156,11 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>菓子類</t>
+          <t>ゼリー飲料3点</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2337</v>
+        <v>878</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -1179,48 +1183,116 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
+          <t>セブンイレブン菅平高原八店</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>内訳記載なし（クレジット払い）</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>14631</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>畠山</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>品目不明。要メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>セブンイレブン菅平高原八店</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>菓子類</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>2337</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>畠山</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>菅平ホテル</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>コインランドリーカード 1000円×2枚</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>畠山</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>残額は翌年繰越。カード現物は部で保管</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="D9" s="1" t="inlineStr">
+    <row r="11">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>雑費 合計</t>
         </is>
       </c>
-      <c r="E9" s="12">
-        <f>SUM(E4:E8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>※ 今年度は5件。昨年度は雑費36件の記録があり、比較して記録漏れがないか確認してください。</t>
+      <c r="E11" s="12">
+        <f>SUM(E4:E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>※ 今年度は7件。昨年度は雑費36件の記録があり、比較して記録漏れがないか確認してください。</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1326,24 +1398,24 @@
     </row>
     <row r="5">
       <c r="A5" s="16" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>セブンイレブン菅平高原八店</t>
+          <t>医療機関</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>串団子3本入 23パック</t>
+          <t>秋元翔斗 受診料</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>3179</v>
+        <v>1070</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>畠山</t>
+          <t>占部</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -1353,89 +1425,23 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>手土産か補食か要確認</t>
+          <t>メディカル費</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>46236</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>セブンイレブン菅平高原八店</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>串団子3本入 5パック</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>691</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>畠山</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>手土産か補食か要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>医療機関</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>秋元翔斗 受診料</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1070</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>占部</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>メディカル費</t>
-        </is>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>父母会予算 合計</t>
+        </is>
+      </c>
+      <c r="D6" s="12">
+        <f>SUM(D4:D5)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>父母会予算 合計</t>
-        </is>
-      </c>
-      <c r="D8" s="12">
-        <f>SUM(D4:D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>※ 対戦校への手土産代・メディカル費等。合宿費（会計分類C）の徴収額には混ぜず、父母会予算から別途精算します。</t>
         </is>
